--- a/班务相关/班委表.xlsx
+++ b/班务相关/班委表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\学校用\大学\网安拔尖班资料\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\学校用\大学\网安拔尖班资料\班务相关\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AFC10C6-9237-4D99-809E-4A049439F5AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E78B21E3-7B6E-4682-AEC3-5DFBAE10ED37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4392" yWindow="1344" windowWidth="17148" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>职务</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -40,10 +40,6 @@
   </si>
   <si>
     <t>杨天霖</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>电话</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -440,118 +436,88 @@
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.6640625" customWidth="1"/>
-    <col min="3" max="3" width="14.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="8.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1">
-        <v>13691017897</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1">
-        <v>15243206766</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="1">
-        <v>13402886668</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1">
-        <v>13210105703</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="B6" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="1">
-        <v>18546407001</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="B7" t="s">
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="1">
-        <v>13767408144</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>15</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="1">
-        <v>13897436629</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>16</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>19</v>
-      </c>
-      <c r="C9" s="1">
-        <v>18997730501</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="1">
-        <v>15839825602</v>
       </c>
     </row>
   </sheetData>
